--- a/data/controles_results/difmedias_dep_vars_tot.xlsx
+++ b/data/controles_results/difmedias_dep_vars_tot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>3300</t>
+    <t>3297</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -87,7 +87,7 @@
     <t>0.009</t>
   </si>
   <si>
-    <t>284</t>
+    <t>287</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -96,22 +96,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>0.277</t>
+    <t>0.276</t>
   </si>
   <si>
     <t>(0.008)</t>
   </si>
   <si>
-    <t>0.280</t>
+    <t>0.279</t>
   </si>
   <si>
     <t>0.003</t>
   </si>
   <si>
-    <t>0.503</t>
-  </si>
-  <si>
-    <t>(0.016)</t>
+    <t>0.505</t>
+  </si>
+  <si>
+    <t>(0.015)</t>
+  </si>
+  <si>
+    <t>0.010</t>
   </si>
   <si>
     <t>(0.002)</t>
@@ -129,16 +132,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>0.019</t>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>0.018</t>
   </si>
   <si>
     <t>0.002**</t>
   </si>
   <si>
-    <t>0.259***</t>
+    <t>0.261***</t>
   </si>
   <si>
     <t>-0.002</t>
@@ -208,7 +211,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -231,7 +234,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -254,7 +257,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -274,10 +277,10 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -320,10 +323,10 @@
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -366,10 +369,10 @@
         <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -412,10 +415,10 @@
         <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -458,10 +461,10 @@
         <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -501,10 +504,10 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -524,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
